--- a/input/Login_SSH_List.xlsx
+++ b/input/Login_SSH_List.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14200"/>
+    <workbookView windowWidth="29868" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="14">
   <si>
     <t>host</t>
   </si>
@@ -43,16 +43,34 @@
     <t>password</t>
   </si>
   <si>
-    <t>192.168.17.128</t>
+    <t>10.10.30.13</t>
   </si>
   <si>
     <t>root</t>
   </si>
   <si>
-    <t>123@.com</t>
-  </si>
-  <si>
-    <t>192.168.17.129</t>
+    <t>Genew@123</t>
+  </si>
+  <si>
+    <t>10.10.30.14</t>
+  </si>
+  <si>
+    <t>10.10.30.55</t>
+  </si>
+  <si>
+    <t>10.10.30.56</t>
+  </si>
+  <si>
+    <t>10.10.30.59</t>
+  </si>
+  <si>
+    <t>10.10.30.60</t>
+  </si>
+  <si>
+    <t>10.10.30.68</t>
+  </si>
+  <si>
+    <t>10.10.30.69</t>
   </si>
 </sst>
 </file>
@@ -697,7 +715,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1011,11 +1029,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="3"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="20.3727272727273" customWidth="1"/>
-    <col min="3" max="4" width="10.3636363636364" customWidth="1"/>
+    <col min="1" max="1" width="20.3703703703704" customWidth="1"/>
+    <col min="3" max="3" width="10.3611111111111" customWidth="1"/>
+    <col min="4" max="4" width="22.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1060,10 +1079,130 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="123@.com"/>
-    <hyperlink ref="D3" r:id="rId1" display="123@.com"/>
+    <hyperlink ref="D2" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
+    <hyperlink ref="D3" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
+    <hyperlink ref="D4" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
+    <hyperlink ref="D5" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
+    <hyperlink ref="D6" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
+    <hyperlink ref="D7" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
+    <hyperlink ref="D8" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
+    <hyperlink ref="D9" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
+    <hyperlink ref="D10" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
+    <hyperlink ref="D11" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1075,7 +1214,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1087,7 +1226,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/input/Login_SSH_List.xlsx
+++ b/input/Login_SSH_List.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
   <si>
     <t>host</t>
   </si>
@@ -43,7 +43,7 @@
     <t>password</t>
   </si>
   <si>
-    <t>10.10.30.13</t>
+    <t>10.10.50.13</t>
   </si>
   <si>
     <t>root</t>
@@ -52,25 +52,28 @@
     <t>Genew@123</t>
   </si>
   <si>
-    <t>10.10.30.14</t>
-  </si>
-  <si>
-    <t>10.10.30.55</t>
-  </si>
-  <si>
-    <t>10.10.30.56</t>
-  </si>
-  <si>
-    <t>10.10.30.59</t>
-  </si>
-  <si>
-    <t>10.10.30.60</t>
-  </si>
-  <si>
-    <t>10.10.30.68</t>
-  </si>
-  <si>
-    <t>10.10.30.69</t>
+    <t>10.10.50.14</t>
+  </si>
+  <si>
+    <t>10.10.50.55</t>
+  </si>
+  <si>
+    <t>10.10.50.56</t>
+  </si>
+  <si>
+    <t>10.10.50.59</t>
+  </si>
+  <si>
+    <t>10.10.50.60</t>
+  </si>
+  <si>
+    <t>10.10.50.68</t>
+  </si>
+  <si>
+    <t>wacos1234</t>
+  </si>
+  <si>
+    <t>10.10.50.69</t>
   </si>
 </sst>
 </file>
@@ -83,7 +86,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +103,13 @@
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
@@ -581,134 +591,134 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -716,6 +726,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1029,7 +1042,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20.3703703703704" customWidth="1"/>
@@ -1137,7 +1150,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>22</v>
@@ -1145,13 +1158,13 @@
       <c r="C8" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>6</v>
+      <c r="D8" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>22</v>
@@ -1159,36 +1172,8 @@
       <c r="C9" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
+      <c r="D9" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="B11">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1199,10 +1184,8 @@
     <hyperlink ref="D5" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
     <hyperlink ref="D6" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
     <hyperlink ref="D7" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
-    <hyperlink ref="D8" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
-    <hyperlink ref="D9" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
-    <hyperlink ref="D10" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
-    <hyperlink ref="D11" r:id="rId1" display="Genew@123" tooltip="mailto:Genew@123"/>
+    <hyperlink ref="D8" r:id="rId1" display="wacos1234" tooltip="mailto:Genew@123"/>
+    <hyperlink ref="D9" r:id="rId1" display="wacos1234" tooltip="mailto:Genew@123"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/input/Login_SSH_List.xlsx
+++ b/input/Login_SSH_List.xlsx
@@ -43,7 +43,7 @@
     <t>password</t>
   </si>
   <si>
-    <t>10.10.50.13</t>
+    <t>10.10.40.13</t>
   </si>
   <si>
     <t>root</t>
@@ -52,28 +52,28 @@
     <t>Genew@123</t>
   </si>
   <si>
-    <t>10.10.50.14</t>
-  </si>
-  <si>
-    <t>10.10.50.55</t>
-  </si>
-  <si>
-    <t>10.10.50.56</t>
-  </si>
-  <si>
-    <t>10.10.50.59</t>
-  </si>
-  <si>
-    <t>10.10.50.60</t>
-  </si>
-  <si>
-    <t>10.10.50.68</t>
+    <t>10.10.40.14</t>
+  </si>
+  <si>
+    <t>10.10.40.55</t>
+  </si>
+  <si>
+    <t>10.10.40.56</t>
+  </si>
+  <si>
+    <t>10.10.40.59</t>
+  </si>
+  <si>
+    <t>10.10.40.60</t>
+  </si>
+  <si>
+    <t>10.10.40.68</t>
   </si>
   <si>
     <t>wacos1234</t>
   </si>
   <si>
-    <t>10.10.50.69</t>
+    <t>10.10.40.69</t>
   </si>
 </sst>
 </file>

--- a/input/Login_SSH_List.xlsx
+++ b/input/Login_SSH_List.xlsx
@@ -43,7 +43,7 @@
     <t>password</t>
   </si>
   <si>
-    <t>10.10.40.13</t>
+    <t>10.10.30.13</t>
   </si>
   <si>
     <t>root</t>
@@ -52,28 +52,28 @@
     <t>Genew@123</t>
   </si>
   <si>
-    <t>10.10.40.14</t>
-  </si>
-  <si>
-    <t>10.10.40.55</t>
-  </si>
-  <si>
-    <t>10.10.40.56</t>
-  </si>
-  <si>
-    <t>10.10.40.59</t>
-  </si>
-  <si>
-    <t>10.10.40.60</t>
-  </si>
-  <si>
-    <t>10.10.40.68</t>
+    <t>10.10.30.14</t>
+  </si>
+  <si>
+    <t>10.10.30.55</t>
+  </si>
+  <si>
+    <t>10.10.30.56</t>
+  </si>
+  <si>
+    <t>10.10.30.59</t>
+  </si>
+  <si>
+    <t>10.10.30.60</t>
+  </si>
+  <si>
+    <t>10.10.30.68</t>
   </si>
   <si>
     <t>wacos1234</t>
   </si>
   <si>
-    <t>10.10.40.69</t>
+    <t>10.10.30.69</t>
   </si>
 </sst>
 </file>
